--- a/naver-place-crawler/results_health/기장군_PT.xlsx
+++ b/naver-place-crawler/results_health/기장군_PT.xlsx
@@ -559,39 +559,39 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>필라테스</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>바디채널 정관점</t>
+          <t>한빛 발레필라테스</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>y1gym@naver.com</t>
+          <t>oopsmomai@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1329-6911</t>
+          <t>051-714-7103</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 정관읍 정관중앙로 45 탑스퀘어 13층 바디채널 부산정관점</t>
+          <t>부산광역시 기장군 장안읍 고무로 328 2층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/y1gym</t>
+          <t>http://pf.kakao.com/_xhlCHxb</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -612,7 +612,7 @@
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>106</v>
+        <v>74</v>
       </c>
       <c r="Q2" t="n">
-        <v>318</v>
+        <v>5</v>
       </c>
       <c r="R2" t="n">
-        <v>424</v>
+        <v>79</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,51 +636,51 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1843679345</t>
+          <t>1434473357</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1843679345</t>
+          <t>https://m.place.naver.com/place/1434473357</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>정관 탑피티짐</t>
+          <t>젬마짐 기장점 헬스&amp;PT</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>guihoooooo@naver.com</t>
+          <t>gemmagym@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1442-9594</t>
+          <t>0507-1395-1517</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 정관읍 정관로 595 정관테라스상가 512호, 513호</t>
+          <t>부산광역시 기장군 기장읍 차성로 314 3층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/guihoooooo</t>
+          <t>https://blog.naver.com/gemmagym</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>30</v>
+        <v>243</v>
       </c>
       <c r="Q3" t="n">
-        <v>62</v>
+        <v>603</v>
       </c>
       <c r="R3" t="n">
-        <v>92</v>
+        <v>846</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,17 +730,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2046901119</t>
+          <t>1331784711</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2046901119</t>
+          <t>https://m.place.naver.com/place/1331784711</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -752,29 +752,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>프로짐 헬스&amp;PT 일광점</t>
+          <t>바벨하우스 정관본점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>progym_ilgwang@naver.com</t>
+          <t>justough@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1315-9249</t>
+          <t>0507-1325-1852</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 일광읍 해빛1로 5 4층 401호, 402호</t>
+          <t>부산광역시 기장군 정관읍 매학용수로 12-1 바벨하우스</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/progym_ilgwang</t>
+          <t>https://blog.naver.com/justough</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -805,17 +805,17 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="Q4" t="n">
-        <v>92</v>
+        <v>161</v>
       </c>
       <c r="R4" t="n">
-        <v>133</v>
+        <v>217</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -824,51 +824,51 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2064071944</t>
+          <t>1886732620</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2064071944</t>
+          <t>https://m.place.naver.com/place/1886732620</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>에잇에잇 그룹PT</t>
+          <t>바디채널 정관점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>roi0890@naver.com</t>
+          <t>y1gym@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>070-8806-5888</t>
+          <t>0507-1329-6911</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>부산광역시 수영구 구락로 110 1층</t>
+          <t>부산광역시 기장군 정관읍 정관중앙로 45 탑스퀘어 13층 바디채널 부산정관점</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/88.functional_fit</t>
+          <t>https://blog.naver.com/y1gym</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -894,7 +894,7 @@
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -903,13 +903,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>173</v>
+        <v>107</v>
       </c>
       <c r="Q5" t="n">
-        <v>121</v>
+        <v>338</v>
       </c>
       <c r="R5" t="n">
-        <v>294</v>
+        <v>445</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -918,17 +918,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1481864298</t>
+          <t>1843679345</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1481864298</t>
+          <t>https://m.place.naver.com/place/1843679345</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -940,29 +940,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>쌤트</t>
+          <t>몽키짐</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>cemtfitness@naver.com</t>
+          <t>dksxkrndl@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>051-710-9679</t>
+          <t>051-728-2904</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 정관읍 정관2로 39-22 헤어샵 2층 쌤트</t>
+          <t>부산광역시 기장군 정관읍 정관4로 39 제이스타워 2층 몽키짐</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/cemtfitness</t>
+          <t>https://blog.naver.com/dksxkrndl</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Q6" t="n">
-        <v>3</v>
+        <v>380</v>
       </c>
       <c r="R6" t="n">
-        <v>3</v>
+        <v>391</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1012,56 +1012,56 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1278346618</t>
+          <t>1341686859</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1278346618</t>
+          <t>https://m.place.naver.com/place/1341686859</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>필라테스클리닉 일광점</t>
+          <t>정관 탑피티짐</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>pilates_clinic@naver.com</t>
+          <t>guihoooooo@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1311-3362</t>
+          <t>0507-1442-9594</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 일광읍 해빛로 17 네오더퍼스트 5층</t>
+          <t>부산광역시 기장군 정관읍 정관로 595 정관테라스상가 512호, 513호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>http://pilatesclinic.kr</t>
+          <t>https://blog.naver.com/guihoooooo</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1091,13 +1091,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>198</v>
+        <v>31</v>
       </c>
       <c r="Q7" t="n">
-        <v>120</v>
+        <v>63</v>
       </c>
       <c r="R7" t="n">
-        <v>318</v>
+        <v>94</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1106,56 +1106,56 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1919807433</t>
+          <t>2046901119</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1919807433</t>
+          <t>https://m.place.naver.com/place/2046901119</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>정관EMS트레이닝</t>
+          <t>림휘트니스</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>regal0000@naver.com</t>
+          <t>limfitness@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1413-7567</t>
+          <t>0507-1349-7885</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 정관읍 정관로 501-11 에이스프라자 2층 202호 이지핏 스튜디오 정관점</t>
+          <t>부산광역시 기장군 기장읍 읍내로 49 탑마트 2층 림휘트니스</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/sKE4gLO</t>
+          <t>https://blog.naver.com/limfitness</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1176,22 +1176,22 @@
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="Q8" t="n">
-        <v>15</v>
+        <v>176</v>
       </c>
       <c r="R8" t="n">
-        <v>22</v>
+        <v>187</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1200,60 +1200,56 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1318823068</t>
+          <t>1074082825</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1318823068</t>
+          <t>https://m.place.naver.com/place/1074082825</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>제로키니 그룹PT 일광점</t>
+          <t>위헬스 장산역점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>pmk060@naver.com</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>jys@zerokini.co.kr</t>
-        </is>
-      </c>
+          <t>wehealthjangsan@naver.com</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1397-5606</t>
+          <t>1800-8273</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 일광읍 해빛로 39-30 5층</t>
+          <t>부산광역시 해운대구 세실로 45 2층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.zerokini.co.kr</t>
+          <t>https://smartstore.naver.com/wehealth_jangsan</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1263,7 +1259,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1274,7 +1270,7 @@
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1283,13 +1279,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>65</v>
+        <v>234</v>
       </c>
       <c r="Q9" t="n">
-        <v>13</v>
+        <v>539</v>
       </c>
       <c r="R9" t="n">
-        <v>78</v>
+        <v>773</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1298,51 +1294,51 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2003643168</t>
+          <t>1867376356</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2003643168</t>
+          <t>https://m.place.naver.com/place/1867376356</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>체력단련,운동</t>
+          <t>축구교실</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>피티박스 정관점</t>
+          <t>이벡스퍼포먼스트레이닝</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>allley_0610@naver.com</t>
+          <t>evex_performance@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1392-2724</t>
+          <t>0507-1412-1932</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 정관읍 모전1길 6-37 3층 301호</t>
+          <t>부산광역시 기장군 정관읍 산단5로 76-142 1층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/evex_performance/</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1352,7 +1348,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1373,17 +1369,17 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="Q10" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>99</v>
+        <v>24</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1392,17 +1388,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1602376352</t>
+          <t>1461291785</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1602376352</t>
+          <t>https://m.place.naver.com/place/1461291785</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1414,29 +1410,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>바벨하우스 정관본점</t>
+          <t>정관PT&amp;헬스 라스트짐</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>justough@naver.com</t>
+          <t>cyh0817123@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1325-1852</t>
+          <t>0507-1327-4965</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 정관읍 매학용수로 12-1 바벨하우스</t>
+          <t>부산광역시 기장군 정관읍 정관7로 33-8 3층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/justough</t>
+          <t>https://www.instagram.com/lastgym_official</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1451,7 +1447,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1471,13 +1467,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>56</v>
+        <v>98</v>
       </c>
       <c r="Q11" t="n">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="R11" t="n">
-        <v>217</v>
+        <v>267</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1486,56 +1482,56 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1886732620</t>
+          <t>2022710913</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1886732620</t>
+          <t>https://m.place.naver.com/place/2022710913</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>젬마짐 기장점 헬스&amp;PT</t>
+          <t>엠씨피트니스&amp;기구필라테스 연산점</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>gemmagym@naver.com</t>
+          <t>mcfitnessyeonsan@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-1395-1517</t>
+          <t>0507-1421-0460</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 기장읍 차성로 314 3층</t>
+          <t>부산광역시 연제구 과정로 152 연산빌딩 3층</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/gemmagym</t>
+          <t>http://pf.kakao.com/_gdRSs/chat</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1545,7 +1541,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1556,7 +1552,7 @@
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1565,13 +1561,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>239</v>
+        <v>1100</v>
       </c>
       <c r="Q12" t="n">
-        <v>603</v>
+        <v>791</v>
       </c>
       <c r="R12" t="n">
-        <v>842</v>
+        <v>1891</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1580,17 +1576,17 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1331784711</t>
+          <t>1678635952</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1331784711</t>
+          <t>https://m.place.naver.com/place/1678635952</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1602,29 +1598,29 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>일광 베베짐 헬스&amp;PT</t>
+          <t>운동J GYM</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>bebe_gym_@naver.com</t>
+          <t>tkdalsrh159@naver.com</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0507-1368-5896</t>
+          <t>051-728-2884</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 일광읍 해빛1로 74 일광골드타워6층 베베짐</t>
+          <t>부산광역시 기장군 정관읍 정관로 579 스타빌딩 3층 306호</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/bebe_gym_</t>
+          <t>https://blog.naver.com/tkdalsrh159</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1659,13 +1655,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>168</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>259</v>
+        <v>99</v>
       </c>
       <c r="R13" t="n">
-        <v>427</v>
+        <v>99</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -1674,51 +1670,51 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>1649149107</t>
+          <t>1204720257</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1649149107</t>
+          <t>https://m.place.naver.com/place/1204720257</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>림휘트니스</t>
+          <t>팔로우짐</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>limfitness@naver.com</t>
+          <t>followpt2021@naver.com</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0507-1349-7885</t>
+          <t>051-724-0250</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 기장읍 읍내로 49 탑마트 2층 림휘트니스</t>
+          <t>부산광역시 기장군 기장읍 차성로288번길 50 3층 팔로우짐</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/limfitness</t>
+          <t>http://followgym.ad-media.kr/</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1733,7 +1729,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1753,13 +1749,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>11</v>
+        <v>77</v>
       </c>
       <c r="Q14" t="n">
-        <v>176</v>
+        <v>64</v>
       </c>
       <c r="R14" t="n">
-        <v>187</v>
+        <v>141</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
@@ -1768,51 +1764,51 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>1074082825</t>
+          <t>1300089002</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1074082825</t>
+          <t>https://m.place.naver.com/place/1300089002</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>정관 나무필라테스</t>
+          <t>와일드플라워짐</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>namoo_pilates@naver.com</t>
+          <t>birthday0116@naver.com</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0507-1400-1930</t>
+          <t>0507-1380-7183</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 정관읍 정관로 574 조은시티 2층 201호</t>
+          <t>부산광역시 기장군 일광읍 해송2로 11 4층 401~404호</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/namoo_pilates/?hl=ko</t>
+          <t>https://www.instagram.com/govalue_</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1847,13 +1843,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>100</v>
+        <v>9</v>
       </c>
       <c r="Q15" t="n">
-        <v>475</v>
+        <v>82</v>
       </c>
       <c r="R15" t="n">
-        <v>575</v>
+        <v>91</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
@@ -1862,51 +1858,47 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>1897617764</t>
+          <t>1733993979</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1897617764</t>
+          <t>https://m.place.naver.com/place/1733993979</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>젬마짐 일광점 헬스&amp;PT</t>
+          <t>힐링짐 PT센터 수영점</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>gemmagym@naver.com</t>
+          <t>healinggym95@naver.com</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>0507-1310-9887</t>
-        </is>
-      </c>
+      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 일광읍 해빛5로 25 센트럴타워 9층</t>
+          <t>부산광역시 수영구 연수로 399 7층</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/gemmagym</t>
+          <t>https://blog.naver.com/healinggym95</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1941,13 +1933,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1135</v>
+        <v>131</v>
       </c>
       <c r="Q16" t="n">
-        <v>1063</v>
+        <v>233</v>
       </c>
       <c r="R16" t="n">
-        <v>2198</v>
+        <v>364</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -1956,51 +1948,51 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>1354328240</t>
+          <t>1645332186</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1354328240</t>
+          <t>https://m.place.naver.com/place/1645332186</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>헬짐 헬스&amp;PT 센텀시티점</t>
+          <t>몽키짐 헬스&amp;PT 일광점</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>hellgym_centum@naver.com</t>
+          <t>monkeygym_@naver.com</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0507-1494-3739</t>
+          <t>0507-1482-0688</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>부산광역시 해운대구 해운대로 335 6층</t>
+          <t>부산광역시 기장군 일광읍 해빛3로 122 6층</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/hellgym_centum</t>
+          <t>https://www.instagram.com/monkey_gym3?igsh=a2lqZHQ2anFucXQ0</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2015,7 +2007,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -2035,13 +2027,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>460</v>
+        <v>434</v>
       </c>
       <c r="Q17" t="n">
-        <v>1235</v>
+        <v>342</v>
       </c>
       <c r="R17" t="n">
-        <v>1695</v>
+        <v>776</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
@@ -2050,17 +2042,17 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>1986332432</t>
+          <t>1842714113</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1986332432</t>
+          <t>https://m.place.naver.com/place/1842714113</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -2072,29 +2064,29 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>나인핏피티</t>
+          <t>포유피티스튜디오 일광점</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>hschoia@naver.com</t>
+          <t>chdnagkrk@naver.com</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0507-1442-9177</t>
+          <t>0507-1391-9431</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 정관읍 정관로 569 제일타워1 2층 206호</t>
+          <t>부산광역시 기장군 일광읍 해빛로 17 4층 403호</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/hschoia</t>
+          <t>https://blog.naver.com/chdnagkrk</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2120,7 +2112,7 @@
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -2129,13 +2121,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>8</v>
+        <v>46</v>
       </c>
       <c r="Q18" t="n">
-        <v>25</v>
+        <v>119</v>
       </c>
       <c r="R18" t="n">
-        <v>33</v>
+        <v>165</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -2144,51 +2136,51 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>1701903877</t>
+          <t>1755922289</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1701903877</t>
+          <t>https://m.place.naver.com/place/1755922289</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>더핏피트니스</t>
+          <t>퀄리티핏</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>4ng4ngup@naver.com</t>
+          <t>highfit1@naver.com</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0507-1412-2460</t>
+          <t>0507-1449-8054</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 정관읍 정관2로 51-27 5층</t>
+          <t>부산광역시 해운대구 해운대로 216 4층 퀄리티핏</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/4ng4ngup</t>
+          <t>https://www.instagram.com/qualityfit_official</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2203,7 +2195,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -2214,7 +2206,7 @@
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -2223,13 +2215,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>59</v>
+        <v>1</v>
       </c>
       <c r="Q19" t="n">
-        <v>388</v>
+        <v>227</v>
       </c>
       <c r="R19" t="n">
-        <v>447</v>
+        <v>228</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -2238,51 +2230,51 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>35432450</t>
+          <t>1217275494</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/35432450</t>
+          <t>https://m.place.naver.com/place/1217275494</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>필라테스</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>그래비티짐 해운대 장산점</t>
+          <t>메디앤컬필라테스 정관점</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>acmilan0@naver.com</t>
+          <t>medincurljeonggwan@naver.com</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0507-1397-0149</t>
+          <t>0507-1437-2824</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>부산광역시 해운대구 해운대로 802 웅신시네아트 A동 6층</t>
+          <t>부산광역시 기장군 정관읍 정관로 563 광장메디컬 5층</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/acmilan0</t>
+          <t>https://blog.naver.com/medincurljeonggwan</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2317,13 +2309,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>475</v>
+        <v>371</v>
       </c>
       <c r="Q20" t="n">
-        <v>149</v>
+        <v>116</v>
       </c>
       <c r="R20" t="n">
-        <v>624</v>
+        <v>487</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
@@ -2332,51 +2324,51 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>1743697484</t>
+          <t>1558955764</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1743697484</t>
+          <t>https://m.place.naver.com/place/1558955764</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>스포츠센터</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>대한휘트니스</t>
+          <t>더힐튼피트니스</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>hyesook6354@naver.com</t>
+          <t>luxurynhouse@naver.com</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0507-1419-1066</t>
+          <t>0507-1352-3745</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 정관읍 정관로 570</t>
+          <t>부산광역시 기장군 정관읍 정관로 575-3 정관제일타워2 8층</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/thehiltonfitness/</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2386,7 +2378,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -2407,17 +2399,17 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
@@ -2426,61 +2418,61 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>38737056</t>
+          <t>1277414329</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38737056</t>
+          <t>https://m.place.naver.com/place/1277414329</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>필라테스</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>더플래닛짐 헬스&amp;PT 해운대 장산역점</t>
+          <t>나무필라테스 일광점</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>theplanetgym@naver.com</t>
+          <t>namoo_pilates@naver.com</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0507-1310-5564</t>
+          <t>0507-1342-0322</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>부산광역시 해운대구 세실로 77 성부빌딩 8층</t>
+          <t>부산광역시 기장군 일광읍 해빛로 13 7층 702호</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1992573620</t>
+          <t>https://blog.naver.com/namoo_pilates</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -2501,17 +2493,17 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P22" t="n">
-        <v>191</v>
+        <v>95</v>
       </c>
       <c r="Q22" t="n">
-        <v>273</v>
+        <v>87</v>
       </c>
       <c r="R22" t="n">
-        <v>464</v>
+        <v>182</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
@@ -2520,51 +2512,51 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>1992573620</t>
+          <t>1856124982</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1992573620</t>
+          <t>https://m.place.naver.com/place/1856124982</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>나무필라테스 일광점</t>
+          <t>쌤트</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>namoo_pilates@naver.com</t>
+          <t>cemtfitness@naver.com</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0507-1342-0322</t>
+          <t>051-710-9679</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 일광읍 해빛로 13 7층 702호</t>
+          <t>부산광역시 기장군 정관읍 정관2로 39-22 헤어샵 2층 쌤트</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/namoo_pilates</t>
+          <t>https://blog.naver.com/cemtfitness</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2599,13 +2591,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>81</v>
+        <v>3</v>
       </c>
       <c r="R23" t="n">
-        <v>175</v>
+        <v>3</v>
       </c>
       <c r="S23" t="inlineStr">
         <is>
@@ -2614,51 +2606,51 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>1856124982</t>
+          <t>1278346618</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1856124982</t>
+          <t>https://m.place.naver.com/place/1278346618</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>필라테스</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>헬스달리아 부산기장점</t>
+          <t>마루필라테스&amp;PT 정관점</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>healthdahlia_pilates@naver.com</t>
+          <t>marupilates-@naver.com</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0507-1349-4454</t>
+          <t>0507-1441-9374</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 기장읍 차성동로126번길 23 1F 헬스달리아</t>
+          <t>부산광역시 기장군 정관읍 정관로 383 2층</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/healthdahlia_pilates</t>
+          <t>https://blog.naver.com/marupilates-/224004135618</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2693,13 +2685,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>574</v>
+        <v>42</v>
       </c>
       <c r="Q24" t="n">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="R24" t="n">
-        <v>662</v>
+        <v>116</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
@@ -2708,17 +2700,17 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>1638524445</t>
+          <t>2014397367</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1638524445</t>
+          <t>https://m.place.naver.com/place/2014397367</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -2730,29 +2722,29 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>위헬스 장산역점</t>
+          <t>WS피트니스</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>wehealthjangsan@naver.com</t>
+          <t>jeg7459@naver.com</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1800-8273</t>
+          <t>0507-1355-7459</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>부산광역시 해운대구 세실로 45 2층</t>
+          <t>부산광역시 해운대구 센텀5로 55 207, 208, 209호</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://smartstore.naver.com/wehealth_jangsan</t>
+          <t>https://www.instagram.com/ws_fitness_centum</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2787,13 +2779,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>230</v>
+        <v>213</v>
       </c>
       <c r="Q25" t="n">
-        <v>536</v>
+        <v>485</v>
       </c>
       <c r="R25" t="n">
-        <v>766</v>
+        <v>698</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
@@ -2802,51 +2794,51 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>1867376356</t>
+          <t>1750481945</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1867376356</t>
+          <t>https://m.place.naver.com/place/1750481945</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>필라테스</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>고앤고짐</t>
+          <t>정관 나무필라테스</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>tobirys@naver.com</t>
+          <t>namoo_pilates@naver.com</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>0507-1353-0350</t>
+          <t>0507-1400-1930</t>
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>부산광역시 수영구 연수로 386 3층 고앤고짐</t>
+          <t>부산광역시 기장군 정관읍 정관로 574 조은시티 2층 201호</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/goandgo_gym</t>
+          <t>https://www.instagram.com/namoo_pilates/?hl=ko</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2881,13 +2873,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="Q26" t="n">
-        <v>63</v>
+        <v>465</v>
       </c>
       <c r="R26" t="n">
-        <v>154</v>
+        <v>566</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
@@ -2896,17 +2888,17 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>1645006111</t>
+          <t>1897617764</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1645006111</t>
+          <t>https://m.place.naver.com/place/1897617764</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -2923,7 +2915,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>sweetie114@naver.com</t>
+          <t>mysowon1004@naver.com</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -3000,7 +2992,7 @@
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -3012,29 +3004,29 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>번바디</t>
+          <t>불독짐 정관점 PTXB스피닝 해머스트렝스 오피셜센터</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>dc2452@naver.com</t>
+          <t>bulldoggym_jeonggwan@naver.com</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>0507-1435-3052</t>
+          <t>0507-1412-6900</t>
         </is>
       </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 일광읍 해빛로 39-8 3층 302호</t>
+          <t>부산광역시 기장군 정관읍 모전1길 14 불독짐</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/burnbody25</t>
+          <t>https://www.instagram.com/bulldoggym_jeonggwan</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3060,7 +3052,7 @@
       <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
@@ -3069,13 +3061,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>37</v>
+        <v>136</v>
       </c>
       <c r="Q28" t="n">
-        <v>16</v>
+        <v>545</v>
       </c>
       <c r="R28" t="n">
-        <v>53</v>
+        <v>681</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
@@ -3084,17 +3076,17 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>1268091241</t>
+          <t>1267203367</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1268091241</t>
+          <t>https://m.place.naver.com/place/1267203367</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -3106,34 +3098,34 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>정관PT 스미스 피트니스 헬스장</t>
+          <t>올바른운동 해운대좌동점</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>ptsmithjg@naver.com</t>
+          <t>yesmyt@naver.com</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>0507-1335-5152</t>
+          <t>0507-1391-3259</t>
         </is>
       </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 정관읍 정관8로 28 5F</t>
+          <t>부산광역시 해운대구 좌동순환로 181 5층</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ptsmithjg</t>
+          <t>https://abrtraining.kr/</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3163,13 +3155,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>307</v>
+        <v>278</v>
       </c>
       <c r="Q29" t="n">
-        <v>679</v>
+        <v>547</v>
       </c>
       <c r="R29" t="n">
-        <v>986</v>
+        <v>825</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
@@ -3178,51 +3170,51 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>1097269306</t>
+          <t>1715982137</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1097269306</t>
+          <t>https://m.place.naver.com/place/1715982137</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>박필라 기장점</t>
+          <t>재우스짐</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>parkpila@naver.com</t>
+          <t>n52003@naver.com</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>051-723-0425</t>
+          <t>051-723-8711</t>
         </is>
       </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 일광읍 해빛1로 5 9층 901호</t>
+          <t>부산광역시 기장군 기장읍 차성동로 91 2층 재우스짐</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/_parkpila_</t>
+          <t>https://open.kakao.com/o/s7SB2djg</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3248,22 +3240,22 @@
       <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P30" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="Q30" t="n">
-        <v>113</v>
+        <v>9</v>
       </c>
       <c r="R30" t="n">
-        <v>143</v>
+        <v>54</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
@@ -3272,51 +3264,51 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>1099205668</t>
+          <t>1435737910</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1099205668</t>
+          <t>https://m.place.naver.com/place/1435737910</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>무예,격투기</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>팀매드 정관</t>
+          <t>번바디</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>ll2279ll@naver.com</t>
+          <t>dc2452@naver.com</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>0507-1391-2280</t>
+          <t>0507-1435-3052</t>
         </is>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 정관읍 정관2로 45 4층</t>
+          <t>부산광역시 기장군 일광읍 해빛로 39-8 3층 302호</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/teammad_jeonggwan/</t>
+          <t>https://www.instagram.com/burnbody25</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3342,7 +3334,7 @@
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
@@ -3351,13 +3343,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>7</v>
+        <v>37</v>
       </c>
       <c r="Q31" t="n">
-        <v>120</v>
+        <v>16</v>
       </c>
       <c r="R31" t="n">
-        <v>127</v>
+        <v>53</v>
       </c>
       <c r="S31" t="inlineStr">
         <is>
@@ -3366,17 +3358,17 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>1918980246</t>
+          <t>1268091241</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1918980246</t>
+          <t>https://m.place.naver.com/place/1268091241</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -3388,25 +3380,29 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>TOP PT GYM</t>
+          <t>팀터틀랫 기장일광점</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>topgym1@naver.com</t>
+          <t>teamturtlelat34@naver.com</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>0507-1476-1683</t>
+        </is>
+      </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 정관읍 정관로 595</t>
+          <t>부산광역시 기장군 일광읍 해송1로 25 6층</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/teamturtlelat34</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -3416,12 +3412,12 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -3437,17 +3433,17 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P32" t="n">
-        <v>140</v>
+        <v>29</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>161</v>
       </c>
       <c r="R32" t="n">
-        <v>140</v>
+        <v>190</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
@@ -3456,51 +3452,51 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>1784014744</t>
+          <t>2097039399</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1784014744</t>
+          <t>https://m.place.naver.com/place/2097039399</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>바디&amp;마인드짐 PT 정관점</t>
+          <t>비포엑스휘트니스 PT &amp; 헬스</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>bmgym@naver.com</t>
+          <t>b4xfitness@naver.com</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>0507-1428-2303</t>
+          <t>1588-5095</t>
         </is>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 정관읍 정관로 574 3층 303호</t>
+          <t>부산광역시 기장군 정관읍 정관로 393 롯데프라자5층</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/bmgym</t>
+          <t>https://blog.naver.com/b4xfitness</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -3535,13 +3531,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>126</v>
+        <v>70</v>
       </c>
       <c r="Q33" t="n">
-        <v>155</v>
+        <v>119</v>
       </c>
       <c r="R33" t="n">
-        <v>281</v>
+        <v>189</v>
       </c>
       <c r="S33" t="inlineStr">
         <is>
@@ -3550,51 +3546,51 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>1358217420</t>
+          <t>37921324</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1358217420</t>
+          <t>https://m.place.naver.com/place/37921324</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>라이프헬스</t>
+          <t>바디&amp;마인드짐 PT 정관점</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>4694035@naver.com</t>
+          <t>bmgym@naver.com</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0507-1374-6690</t>
+          <t>0507-1428-2303</t>
         </is>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 기장읍 반송로 1650 라이프온천헬스 4층</t>
+          <t>부산광역시 기장군 정관읍 정관로 574 3층 303호</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/lifesports_official</t>
+          <t>https://blog.naver.com/bmgym</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -3609,7 +3605,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -3629,13 +3625,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>51</v>
+        <v>127</v>
       </c>
       <c r="Q34" t="n">
-        <v>86</v>
+        <v>155</v>
       </c>
       <c r="R34" t="n">
-        <v>137</v>
+        <v>282</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
@@ -3644,17 +3640,17 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>1333260136</t>
+          <t>1358217420</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1333260136</t>
+          <t>https://m.place.naver.com/place/1358217420</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -3666,29 +3662,29 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>포유피티스튜디오 일광점</t>
+          <t>더무브 필라테스 &amp; PT 센텀점</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>chdnagkrk@naver.com</t>
+          <t>themove90@naver.com</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>0507-1391-9431</t>
+          <t>0507-1330-9998</t>
         </is>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 일광읍 해빛로 17 4층 403호</t>
+          <t>부산광역시 해운대구 센텀동로 90 2층 213호, 214호</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/chdnagkrk</t>
+          <t>https://blog.naver.com/themove90</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -3714,22 +3710,22 @@
       <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P35" t="n">
-        <v>46</v>
+        <v>69</v>
       </c>
       <c r="Q35" t="n">
-        <v>130</v>
+        <v>232</v>
       </c>
       <c r="R35" t="n">
-        <v>176</v>
+        <v>301</v>
       </c>
       <c r="S35" t="inlineStr">
         <is>
@@ -3738,17 +3734,17 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>1755922289</t>
+          <t>1839385378</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1755922289</t>
+          <t>https://m.place.naver.com/place/1839385378</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -3760,29 +3756,29 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>정석피트니스 수영점 헬스 PT</t>
+          <t>강해짐 정관점</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>standardpt2@naver.com</t>
+          <t>gang_hae_gym@naver.com</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>0507-1364-4896</t>
+          <t>0507-1303-2889</t>
         </is>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>부산광역시 수영구 수영로 701 선옥빌딩 2, 3층</t>
+          <t>부산광역시 기장군 정관읍 정관로 578 조은타워 7층</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/standardpt2</t>
+          <t>https://blog.naver.com/gang_hae_gym</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -3808,7 +3804,7 @@
       <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
@@ -3817,13 +3813,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>474</v>
+        <v>334</v>
       </c>
       <c r="Q36" t="n">
-        <v>134</v>
+        <v>322</v>
       </c>
       <c r="R36" t="n">
-        <v>608</v>
+        <v>656</v>
       </c>
       <c r="S36" t="inlineStr">
         <is>
@@ -3832,51 +3828,51 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>1050344461</t>
+          <t>1279713302</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1050344461</t>
+          <t>https://m.place.naver.com/place/1279713302</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>무예,격투기</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>몽키짐 헬스&amp;PT 일광점</t>
+          <t>팀매드 정관</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>monkeygym_@naver.com</t>
+          <t>ll2279ll@naver.com</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>0507-1482-0688</t>
+          <t>0507-1391-2280</t>
         </is>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 일광읍 해빛3로 122 6층</t>
+          <t>부산광역시 기장군 정관읍 정관2로 45 4층</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/monkey_gym3?igsh=a2lqZHQ2anFucXQ0</t>
+          <t>https://www.instagram.com/teammad_jeonggwan/</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -3911,13 +3907,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>432</v>
+        <v>7</v>
       </c>
       <c r="Q37" t="n">
-        <v>341</v>
+        <v>120</v>
       </c>
       <c r="R37" t="n">
-        <v>773</v>
+        <v>127</v>
       </c>
       <c r="S37" t="inlineStr">
         <is>
@@ -3926,17 +3922,17 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>1842714113</t>
+          <t>1918980246</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1842714113</t>
+          <t>https://m.place.naver.com/place/1918980246</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -3948,34 +3944,34 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>몸짱스튜디오</t>
+          <t>핏 라이프스타일 해운대</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>oeh8387@naver.com</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>0507-1496-7878</t>
-        </is>
-      </c>
+          <t>tmzjwl27@naver.com</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>isj89858@gmail.com</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 기장읍 차성로344번길 6 3층</t>
+          <t>부산광역시 해운대구 세실로69번길 15 7F 핏 라이프스타일</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>http://cafe.naver.com/smasterclub</t>
+          <t>https://drive.google.com/drive/folders/1FE2ojnmHyYiv3OlukWegw9jtzBYKObAA</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -4001,17 +3997,17 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P38" t="n">
-        <v>1</v>
+        <v>403</v>
       </c>
       <c r="Q38" t="n">
-        <v>7</v>
+        <v>1057</v>
       </c>
       <c r="R38" t="n">
-        <v>8</v>
+        <v>1460</v>
       </c>
       <c r="S38" t="inlineStr">
         <is>
@@ -4020,56 +4016,52 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>33305903</t>
+          <t>1236047384</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/33305903</t>
+          <t>https://m.place.naver.com/place/1236047384</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>엠씨피트니스&amp;기구필라테스 연산점</t>
+          <t>이리스 피트니스</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>mcfitnessyeonsan@naver.com</t>
+          <t>danairis_@naver.com</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>0507-1421-0460</t>
-        </is>
-      </c>
+      <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 과정로 152 연산빌딩 3층</t>
+          <t>부산광역시 기장군 정관읍 정관2로 39-14 7층 이리스피트니스</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_gdRSs/chat</t>
+          <t>https://blog.naver.com/danairis_</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -4079,7 +4071,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -4090,7 +4082,7 @@
       <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
@@ -4099,13 +4091,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>1092</v>
+        <v>14</v>
       </c>
       <c r="Q39" t="n">
-        <v>801</v>
+        <v>8</v>
       </c>
       <c r="R39" t="n">
-        <v>1893</v>
+        <v>22</v>
       </c>
       <c r="S39" t="inlineStr">
         <is>
@@ -4114,51 +4106,51 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>1678635952</t>
+          <t>1706105476</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1678635952</t>
+          <t>https://m.place.naver.com/place/1706105476</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>팔로우짐</t>
+          <t>더핏피트니스</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>followpt2021@naver.com</t>
+          <t>4ng4ngup@naver.com</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>051-724-0250</t>
+          <t>0507-1412-2460</t>
         </is>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 기장읍 차성로288번길 50 3층 팔로우짐</t>
+          <t>부산광역시 기장군 정관읍 정관2로 51-27 5층</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>http://followgym.ad-media.kr/</t>
+          <t>https://blog.naver.com/4ng4ngup</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -4173,7 +4165,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -4193,13 +4185,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>77</v>
+        <v>61</v>
       </c>
       <c r="Q40" t="n">
-        <v>64</v>
+        <v>391</v>
       </c>
       <c r="R40" t="n">
-        <v>141</v>
+        <v>452</v>
       </c>
       <c r="S40" t="inlineStr">
         <is>
@@ -4208,61 +4200,61 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>1300089002</t>
+          <t>35432450</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1300089002</t>
+          <t>https://m.place.naver.com/place/35432450</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>스포츠센터</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>한빛 발레필라테스</t>
+          <t>대한휘트니스</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>oopsmomai@naver.com</t>
+          <t>hyesook6354@naver.com</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>051-714-7103</t>
+          <t>0507-1419-1066</t>
         </is>
       </c>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 장안읍 고무로 328 2층</t>
+          <t>부산광역시 기장군 정관읍 정관로 570</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_xhlCHxb</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -4278,22 +4270,22 @@
       <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P41" t="n">
-        <v>74</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="S41" t="inlineStr">
         <is>
@@ -4302,51 +4294,51 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>1434473357</t>
+          <t>38737056</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1434473357</t>
+          <t>https://m.place.naver.com/place/38737056</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>BB필라테스 일광점</t>
+          <t>건담짐 미국감성프리미엄헬스&amp;PT</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>bbpilates_ilguang@naver.com</t>
+          <t>rlarjsdn12433@naver.com</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>0507-1432-0163</t>
+          <t>0507-1323-5243</t>
         </is>
       </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 일광읍 해송2로 11 미라벨 5층 501, 502호</t>
+          <t>부산광역시 동래구 온천천로 391 1층 건담짐</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/bbpilates_ilguang/</t>
+          <t>https://blog.naver.com/rlarjsdn12433</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -4361,7 +4353,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -4381,13 +4373,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>67</v>
+        <v>2883</v>
       </c>
       <c r="Q42" t="n">
-        <v>103</v>
+        <v>900</v>
       </c>
       <c r="R42" t="n">
-        <v>170</v>
+        <v>3783</v>
       </c>
       <c r="S42" t="inlineStr">
         <is>
@@ -4396,17 +4388,17 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>1281840251</t>
+          <t>1130935293</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1281840251</t>
+          <t>https://m.place.naver.com/place/1130935293</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -4418,29 +4410,29 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>운동J GYM</t>
+          <t>그래비티짐 해운대 장산점</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>tkdalsrh159@naver.com</t>
+          <t>acmilan0@naver.com</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>051-728-2884</t>
+          <t>0507-1397-0149</t>
         </is>
       </c>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 정관읍 정관로 579 스타빌딩 3층 306호</t>
+          <t>부산광역시 해운대구 해운대로 802 웅신시네아트 A동 6층</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/tkdalsrh159</t>
+          <t>https://blog.naver.com/acmilan0</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -4475,13 +4467,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>476</v>
       </c>
       <c r="Q43" t="n">
-        <v>97</v>
+        <v>156</v>
       </c>
       <c r="R43" t="n">
-        <v>97</v>
+        <v>632</v>
       </c>
       <c r="S43" t="inlineStr">
         <is>
@@ -4490,51 +4482,51 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>1204720257</t>
+          <t>1743697484</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1204720257</t>
+          <t>https://m.place.naver.com/place/1743697484</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>장비,기기</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>BT비티아시바피티아시바파이프가설자재판매임대설치</t>
+          <t>하이리페움 피트니스</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>hnco@naver.com</t>
+          <t>high9970@naver.com</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>070-4593-0268</t>
+          <t>070-4222-6939</t>
         </is>
       </c>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 철마면 고촌리</t>
+          <t>부산광역시 기장군 일광읍 해빛4로 35 2층</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://highlifeum.kr</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -4544,7 +4536,7 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -4565,17 +4557,17 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="S44" t="inlineStr">
         <is>
@@ -4584,17 +4576,17 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>1042095191</t>
+          <t>1027296796</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1042095191</t>
+          <t>https://m.place.naver.com/place/1027296796</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -4606,29 +4598,29 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>버킷바디짐 여성전용 프리미엄PT 정관점</t>
+          <t>로운짐</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>bucketbodygym@naver.com</t>
+          <t>roun_gym@naver.com</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>0507-1341-9514</t>
+          <t>0507-1358-0936</t>
         </is>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 정관읍 정관로 561 정관타워 703호 버킷바디짐 여성전문 정관PT</t>
+          <t>부산광역시 기장군 기장읍 차성동로182번길 13 2층 로운짐</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/bucketbodygym</t>
+          <t>https://www.instagram.com/h___jongjin</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -4643,7 +4635,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -4663,13 +4655,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>113</v>
+        <v>175</v>
       </c>
       <c r="Q45" t="n">
-        <v>851</v>
+        <v>321</v>
       </c>
       <c r="R45" t="n">
-        <v>964</v>
+        <v>496</v>
       </c>
       <c r="S45" t="inlineStr">
         <is>
@@ -4678,17 +4670,17 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>1083631392</t>
+          <t>1074349483</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1083631392</t>
+          <t>https://m.place.naver.com/place/1074349483</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -4700,29 +4692,29 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>더스피닝 본점 &amp; PT 연산점</t>
+          <t>노아 ems 스튜디오</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>thespinningyeonsan@naver.com</t>
+          <t>sungminjin1004@naver.com</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
-          <t>0507-1401-8936</t>
+          <t>0507-1473-0247</t>
         </is>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 과정로 190 4층</t>
+          <t>부산광역시 기장군 정관읍 모전1길 6-37</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/thespinning</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -4732,7 +4724,7 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -4753,17 +4745,17 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P46" t="n">
-        <v>426</v>
+        <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>475</v>
+        <v>63</v>
       </c>
       <c r="R46" t="n">
-        <v>901</v>
+        <v>63</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
@@ -4772,51 +4764,51 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>1657255148</t>
+          <t>1895077631</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1657255148</t>
+          <t>https://m.place.naver.com/place/1895077631</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>필라테스</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>와일드플라워짐</t>
+          <t>스미스필라테스&amp;PT 기장점</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>birthday0116@naver.com</t>
+          <t>dpdlk2020@naver.com</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>0507-1380-7183</t>
+          <t>0507-1471-8983</t>
         </is>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 일광읍 해송2로 11 4층 401~404호</t>
+          <t>부산광역시 기장군 기장읍 차성로 430 3층</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/govalue_</t>
+          <t>https://blog.naver.com/dpdlk2020</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -4831,7 +4823,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -4851,13 +4843,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="Q47" t="n">
         <v>80</v>
       </c>
       <c r="R47" t="n">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="S47" t="inlineStr">
         <is>
@@ -4866,51 +4858,51 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>1733993979</t>
+          <t>1629648654</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1733993979</t>
+          <t>https://m.place.naver.com/place/1629648654</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>필라테스</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>강해짐 일광점 헬스&amp;PT</t>
+          <t>필라테스클리닉 일광점</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>gang_hae_gym@naver.com</t>
+          <t>pilates_clinic@naver.com</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
-          <t>0507-1357-1828</t>
+          <t>0507-1311-3362</t>
         </is>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 일광읍 해송4로 16 에코테라스 7층</t>
+          <t>부산광역시 기장군 일광읍 해빛로 17 네오더퍼스트 5층</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>https://pf.kakao.com/_AspkG</t>
+          <t>http://pilatesclinic.kr</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -4925,7 +4917,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -4936,7 +4928,7 @@
       <c r="M48" t="inlineStr"/>
       <c r="N48" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
@@ -4945,13 +4937,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>181</v>
+        <v>196</v>
       </c>
       <c r="Q48" t="n">
-        <v>364</v>
+        <v>120</v>
       </c>
       <c r="R48" t="n">
-        <v>545</v>
+        <v>316</v>
       </c>
       <c r="S48" t="inlineStr">
         <is>
@@ -4960,51 +4952,51 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>1142407899</t>
+          <t>1919807433</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1142407899</t>
+          <t>https://m.place.naver.com/place/1919807433</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>불독짐 정관점 PTXB스피닝 해머스트렝스 오피셜센터</t>
+          <t>라인업 피트니스 헬스&amp;PT</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>bulldoggym_jeonggwan@naver.com</t>
+          <t>ptsmithjg@naver.com</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>0507-1412-6900</t>
+          <t>0507-1335-5152</t>
         </is>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 정관읍 모전1길 14 불독짐</t>
+          <t>부산광역시 기장군 정관읍 정관8로 28 5F</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/bulldoggym_jeonggwan</t>
+          <t>https://blog.naver.com/ptsmithjg</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -5019,7 +5011,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -5039,13 +5031,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>136</v>
+        <v>311</v>
       </c>
       <c r="Q49" t="n">
-        <v>534</v>
+        <v>686</v>
       </c>
       <c r="R49" t="n">
-        <v>670</v>
+        <v>997</v>
       </c>
       <c r="S49" t="inlineStr">
         <is>
@@ -5054,51 +5046,51 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>1267203367</t>
+          <t>1097269306</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1267203367</t>
+          <t>https://m.place.naver.com/place/1097269306</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>폴인기구필라테스&amp;PT 부산 기장점</t>
+          <t>나인핏피티</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>cheryll1@naver.com</t>
+          <t>hschoia@naver.com</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>0507-1434-0830</t>
+          <t>0507-1442-9177</t>
         </is>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 기장읍 차성로 340 명성빌딩 5층</t>
+          <t>부산광역시 기장군 정관읍 정관로 569 제일타워1 2층 206호</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/fallin_gijang</t>
+          <t>https://blog.naver.com/hschoia</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -5113,7 +5105,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -5133,13 +5125,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>154</v>
+        <v>8</v>
       </c>
       <c r="Q50" t="n">
-        <v>477</v>
+        <v>17</v>
       </c>
       <c r="R50" t="n">
-        <v>631</v>
+        <v>25</v>
       </c>
       <c r="S50" t="inlineStr">
         <is>
@@ -5148,17 +5140,17 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>1570283352</t>
+          <t>1701903877</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1570283352</t>
+          <t>https://m.place.naver.com/place/1701903877</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -5170,29 +5162,29 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>보나pt</t>
+          <t>정관EMS트레이닝</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>lzet9@naver.com</t>
+          <t>regal0000@naver.com</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>0507-1385-1049</t>
+          <t>0507-1413-7567</t>
         </is>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 일광읍 해빛6로 99</t>
+          <t>부산광역시 기장군 정관읍 정관로 501-11 에이스프라자 2층 202호 이지핏 스튜디오 정관점</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/sm1fvH4f</t>
+          <t>https://open.kakao.com/o/sKE4gLO</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -5223,17 +5215,17 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P51" t="n">
-        <v>36</v>
+        <v>7</v>
       </c>
       <c r="Q51" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="R51" t="n">
-        <v>54</v>
+        <v>15</v>
       </c>
       <c r="S51" t="inlineStr">
         <is>
@@ -5242,17 +5234,17 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>1704051828</t>
+          <t>1318823068</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1704051828</t>
+          <t>https://m.place.naver.com/place/1318823068</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -5264,29 +5256,29 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>몽키짐</t>
+          <t>에잇에잇 그룹PT</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>dksxkrndl@naver.com</t>
+          <t>suhyu_@naver.com</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>051-728-2904</t>
+          <t>070-8806-5888</t>
         </is>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 정관읍 정관4로 39 제이스타워 2층 몽키짐</t>
+          <t>부산광역시 수영구 구락로 110 1층</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/dksxkrndl</t>
+          <t>https://www.instagram.com/88.functional_fit</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -5301,7 +5293,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -5312,7 +5304,7 @@
       <c r="M52" t="inlineStr"/>
       <c r="N52" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
@@ -5321,13 +5313,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>11</v>
+        <v>173</v>
       </c>
       <c r="Q52" t="n">
-        <v>380</v>
+        <v>123</v>
       </c>
       <c r="R52" t="n">
-        <v>391</v>
+        <v>296</v>
       </c>
       <c r="S52" t="inlineStr">
         <is>
@@ -5336,51 +5328,51 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>1341686859</t>
+          <t>1481864298</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1341686859</t>
+          <t>https://m.place.naver.com/place/1481864298</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>마루필라테스&amp;PT 정관점</t>
+          <t>상상피트니스 정관점</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>marupilates-@naver.com</t>
+          <t>sangsangft1@naver.com</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
-          <t>0507-1441-9374</t>
+          <t>0507-1371-3383</t>
         </is>
       </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 정관읍 정관로 383 2층</t>
+          <t>부산광역시 기장군 정관읍 정관6로 39 메가박스 3층</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/marupilates-/224004135618</t>
+          <t>https://www.instagram.com/sangsang_jeonggwan/</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -5395,7 +5387,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -5415,13 +5407,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>41</v>
+        <v>913</v>
       </c>
       <c r="Q53" t="n">
-        <v>70</v>
+        <v>1229</v>
       </c>
       <c r="R53" t="n">
-        <v>111</v>
+        <v>2142</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
@@ -5430,51 +5422,51 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>2014397367</t>
+          <t>1193206895</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2014397367</t>
+          <t>https://m.place.naver.com/place/1193206895</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>강해짐 정관점</t>
+          <t>더스피닝 본점 &amp; PT 연산점</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>gang_hae_gym@naver.com</t>
+          <t>thespinningyeonsan@naver.com</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
-          <t>0507-1303-2889</t>
+          <t>0507-1401-8936</t>
         </is>
       </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 정관읍 정관로 578 조은타워 7층</t>
+          <t>부산광역시 연제구 과정로 190 4층</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/gang_hae_gym</t>
+          <t>https://www.instagram.com/thespinning</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -5489,7 +5481,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -5500,7 +5492,7 @@
       <c r="M54" t="inlineStr"/>
       <c r="N54" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
@@ -5509,13 +5501,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>331</v>
+        <v>429</v>
       </c>
       <c r="Q54" t="n">
-        <v>323</v>
+        <v>480</v>
       </c>
       <c r="R54" t="n">
-        <v>654</v>
+        <v>909</v>
       </c>
       <c r="S54" t="inlineStr">
         <is>
@@ -5524,51 +5516,51 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>1279713302</t>
+          <t>1657255148</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1279713302</t>
+          <t>https://m.place.naver.com/place/1657255148</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>마이애미짐 센텀점 24시헬스PT</t>
+          <t>젬마짐 일광점 헬스&amp;PT</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>miamigymnc@naver.com</t>
+          <t>gemmagym@naver.com</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>0507-1319-8441</t>
+          <t>0507-1310-9887</t>
         </is>
       </c>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
-          <t>부산광역시 해운대구 센텀중앙로 90 B1</t>
+          <t>부산광역시 기장군 일광읍 해빛5로 25 센트럴타워 9층</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/miamigymnc</t>
+          <t>https://blog.naver.com/gemmagym</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -5603,13 +5595,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>297</v>
+        <v>1137</v>
       </c>
       <c r="Q55" t="n">
-        <v>462</v>
+        <v>1066</v>
       </c>
       <c r="R55" t="n">
-        <v>759</v>
+        <v>2203</v>
       </c>
       <c r="S55" t="inlineStr">
         <is>
@@ -5618,51 +5610,51 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>1160428762</t>
+          <t>1354328240</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1160428762</t>
+          <t>https://m.place.naver.com/place/1354328240</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>로운짐</t>
+          <t>프로짐 헬스&amp;PT 일광점</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>roun_gym@naver.com</t>
+          <t>progym_ilgwang@naver.com</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>0507-1358-0936</t>
+          <t>0507-1315-9249</t>
         </is>
       </c>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 기장읍 차성동로182번길 13 2층 로운짐</t>
+          <t>부산광역시 기장군 일광읍 해빛1로 5 4층 401호, 402호</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/h___jongjin</t>
+          <t>https://blog.naver.com/progym_ilgwang</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -5677,7 +5669,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -5693,17 +5685,17 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P56" t="n">
-        <v>175</v>
+        <v>48</v>
       </c>
       <c r="Q56" t="n">
-        <v>318</v>
+        <v>116</v>
       </c>
       <c r="R56" t="n">
-        <v>493</v>
+        <v>164</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
@@ -5712,51 +5704,51 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>1074349483</t>
+          <t>2064071944</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1074349483</t>
+          <t>https://m.place.naver.com/place/2064071944</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>더힐튼피트니스</t>
+          <t>에스짐 PT&amp;헬스&amp;태닝</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>luxurynhouse@naver.com</t>
+          <t>ifbb1369@naver.com</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>0507-1352-3745</t>
+          <t>0507-1386-3421</t>
         </is>
       </c>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 정관읍 정관로 575-3 정관제일타워2 8층</t>
+          <t>부산광역시 기장군 정관읍 정관로 565 진우빌딩 501호, 601호, 602호</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/thehiltonfitness/</t>
+          <t>https://www.instagram.com/seowone</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -5791,13 +5783,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>26</v>
+        <v>143</v>
       </c>
       <c r="Q57" t="n">
-        <v>3</v>
+        <v>295</v>
       </c>
       <c r="R57" t="n">
-        <v>29</v>
+        <v>438</v>
       </c>
       <c r="S57" t="inlineStr">
         <is>
@@ -5806,51 +5798,51 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>1277414329</t>
+          <t>1668085935</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1277414329</t>
+          <t>https://m.place.naver.com/place/1668085935</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>체력단련,운동</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>팀터틀랫 기장일광점</t>
+          <t>피티박스 정관점</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>teamturtlelat34@naver.com</t>
+          <t>allley_0610@naver.com</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>0507-1476-1683</t>
+          <t>0507-1392-2724</t>
         </is>
       </c>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 일광읍 해송1로 25 6층</t>
+          <t>부산광역시 기장군 정관읍 모전1길 6-37 3층 301호</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/teamturtlelat34</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -5860,12 +5852,12 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -5881,17 +5873,17 @@
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P58" t="n">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="Q58" t="n">
-        <v>158</v>
+        <v>55</v>
       </c>
       <c r="R58" t="n">
-        <v>184</v>
+        <v>99</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
@@ -5900,17 +5892,17 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>2097039399</t>
+          <t>1602376352</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2097039399</t>
+          <t>https://m.place.naver.com/place/1602376352</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -5922,29 +5914,29 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>스미스필라테스&amp;PT 기장점</t>
+          <t>박필라 기장점</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>dpdlk2020@naver.com</t>
+          <t>parkpila@naver.com</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>0507-1471-8983</t>
+          <t>051-723-0425</t>
         </is>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 기장읍 차성로 430 3층</t>
+          <t>부산광역시 기장군 일광읍 해빛1로 5 9층 901호</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/dpdlk2020</t>
+          <t>https://www.instagram.com/_parkpila_</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -5959,7 +5951,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -5979,13 +5971,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="Q59" t="n">
-        <v>79</v>
+        <v>114</v>
       </c>
       <c r="R59" t="n">
-        <v>93</v>
+        <v>145</v>
       </c>
       <c r="S59" t="inlineStr">
         <is>
@@ -5994,51 +5986,51 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>1629648654</t>
+          <t>1099205668</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1629648654</t>
+          <t>https://m.place.naver.com/place/1099205668</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>축구교실</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>이벡스퍼포먼스트레이닝</t>
+          <t>라이프헬스</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>evex_performance@naver.com</t>
+          <t>4694035@naver.com</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
-          <t>0507-1412-1932</t>
+          <t>0507-1374-6690</t>
         </is>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 정관읍 산단5로 76-142 1층</t>
+          <t>부산광역시 기장군 기장읍 반송로 1650 라이프온천헬스 4층</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/evex_performance/</t>
+          <t>https://www.instagram.com/lifesports_official</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -6073,13 +6065,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="Q60" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="R60" t="n">
-        <v>24</v>
+        <v>138</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
@@ -6088,51 +6080,51 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>1461291785</t>
+          <t>1333260136</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1461291785</t>
+          <t>https://m.place.naver.com/place/1333260136</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>에스짐 PT&amp;헬스&amp;태닝</t>
+          <t>몸짱스튜디오</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>ifbb1369@naver.com</t>
+          <t>oeh8387@naver.com</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>0507-1386-3421</t>
+          <t>0507-1496-7878</t>
         </is>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 정관읍 정관로 565 진우빌딩 501호, 601호, 602호</t>
+          <t>부산광역시 기장군 기장읍 차성로344번길 6 3층</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/seowone</t>
+          <t>http://cafe.naver.com/smasterclub</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -6147,7 +6139,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -6163,17 +6155,17 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P61" t="n">
-        <v>143</v>
+        <v>1</v>
       </c>
       <c r="Q61" t="n">
-        <v>286</v>
+        <v>7</v>
       </c>
       <c r="R61" t="n">
-        <v>429</v>
+        <v>8</v>
       </c>
       <c r="S61" t="inlineStr">
         <is>
@@ -6182,52 +6174,56 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>1668085935</t>
+          <t>33305903</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1668085935</t>
+          <t>https://m.place.naver.com/place/33305903</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>핏 라이프스타일 해운대</t>
+          <t>빔스짐</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>tmzjwl27@naver.com</t>
+          <t>vimsgym_3@naver.com</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
-      <c r="E62" t="inlineStr"/>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>0507-1310-1516</t>
+        </is>
+      </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
-          <t>부산광역시 해운대구 세실로69번길 15 7F 핏 라이프스타일</t>
+          <t>부산광역시 해운대구 선수촌로 95 지하1층</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>https://drive.google.com/drive/folders/1FE2ojnmHyYiv3OlukWegw9jtzBYKObAA</t>
+          <t>https://www.instagram.com/vims_gym_3</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -6257,13 +6253,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>403</v>
+        <v>579</v>
       </c>
       <c r="Q62" t="n">
-        <v>1057</v>
+        <v>67</v>
       </c>
       <c r="R62" t="n">
-        <v>1460</v>
+        <v>646</v>
       </c>
       <c r="S62" t="inlineStr">
         <is>
@@ -6272,17 +6268,17 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>1236047384</t>
+          <t>1097711832</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1236047384</t>
+          <t>https://m.place.naver.com/place/1097711832</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -6294,29 +6290,29 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>노아 ems 스튜디오</t>
+          <t>보나pt</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>sungminjin1004@naver.com</t>
+          <t>lzet9@naver.com</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>0507-1473-0247</t>
+          <t>0507-1385-1049</t>
         </is>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 정관읍 모전1길 6-37</t>
+          <t>부산광역시 기장군 일광읍 해빛6로 99</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://open.kakao.com/o/sm1fvH4f</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -6326,7 +6322,7 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -6342,22 +6338,22 @@
       <c r="M63" t="inlineStr"/>
       <c r="N63" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P63" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="Q63" t="n">
-        <v>63</v>
+        <v>18</v>
       </c>
       <c r="R63" t="n">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="S63" t="inlineStr">
         <is>
@@ -6366,17 +6362,17 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>1895077631</t>
+          <t>1704051828</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1895077631</t>
+          <t>https://m.place.naver.com/place/1704051828</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -6445,13 +6441,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="Q64" t="n">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="R64" t="n">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="S64" t="inlineStr">
         <is>
@@ -6470,41 +6466,41 @@
       </c>
       <c r="V64" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>비포엑스휘트니스 PT &amp; 헬스</t>
+          <t>헬짐 헬스&amp;PT 센텀시티점</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>b4xfitness@naver.com</t>
+          <t>hellgym_centum@naver.com</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>1588-5095</t>
+          <t>0507-1494-3739</t>
         </is>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 정관읍 정관로 393 롯데프라자5층</t>
+          <t>부산광역시 해운대구 해운대로 335 6층</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/b4xfitness</t>
+          <t>https://blog.naver.com/hellgym_centum</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -6539,13 +6535,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>70</v>
+        <v>461</v>
       </c>
       <c r="Q65" t="n">
-        <v>119</v>
+        <v>1238</v>
       </c>
       <c r="R65" t="n">
-        <v>189</v>
+        <v>1699</v>
       </c>
       <c r="S65" t="inlineStr">
         <is>
@@ -6554,17 +6550,17 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>37921324</t>
+          <t>1986332432</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37921324</t>
+          <t>https://m.place.naver.com/place/1986332432</t>
         </is>
       </c>
       <c r="V65" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -6576,34 +6572,34 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>재우스짐</t>
+          <t>일광 베베짐 헬스&amp;PT</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>n52003@naver.com</t>
+          <t>bebe_gym_@naver.com</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>051-723-8711</t>
+          <t>0507-1368-5896</t>
         </is>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 기장읍 차성동로 91 2층 재우스짐</t>
+          <t>부산광역시 기장군 일광읍 해빛1로 74 일광골드타워6층 베베짐</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/s7SB2djg</t>
+          <t>https://blog.naver.com/bebe_gym_</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -6613,7 +6609,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -6624,22 +6620,22 @@
       <c r="M66" t="inlineStr"/>
       <c r="N66" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P66" t="n">
-        <v>45</v>
+        <v>168</v>
       </c>
       <c r="Q66" t="n">
-        <v>9</v>
+        <v>263</v>
       </c>
       <c r="R66" t="n">
-        <v>54</v>
+        <v>431</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
@@ -6648,51 +6644,51 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>1435737910</t>
+          <t>1649149107</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1435737910</t>
+          <t>https://m.place.naver.com/place/1649149107</t>
         </is>
       </c>
       <c r="V66" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>건축자재,용품</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>정관PT&amp;헬스 라스트짐</t>
+          <t>송정가설</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>cyh0817123@naver.com</t>
+          <t>xnsjaqj2021@naver.com</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>0507-1327-4965</t>
+          <t>051-723-9927</t>
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 정관읍 정관7로 33-8 3층</t>
+          <t>부산광역시 기장군 기장읍 내리1길 6</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/lastgym_official</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -6702,7 +6698,7 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -6723,17 +6719,17 @@
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P67" t="n">
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>168</v>
+        <v>3</v>
       </c>
       <c r="R67" t="n">
-        <v>265</v>
+        <v>3</v>
       </c>
       <c r="S67" t="inlineStr">
         <is>
@@ -6742,17 +6738,17 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>2022710913</t>
+          <t>37046367</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2022710913</t>
+          <t>https://m.place.naver.com/place/37046367</t>
         </is>
       </c>
       <c r="V67" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -6764,29 +6760,29 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>더무브 필라테스 &amp; PT 센텀점</t>
+          <t>마이애미짐 센텀점 24시헬스PT</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>themove90@naver.com</t>
+          <t>miamigymnc@naver.com</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
-          <t>0507-1330-9998</t>
+          <t>0507-1319-8441</t>
         </is>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
-          <t>부산광역시 해운대구 센텀동로 90 2층 213호, 214호</t>
+          <t>부산광역시 해운대구 센텀중앙로 90 B1</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/themove90</t>
+          <t>https://blog.naver.com/miamigymnc</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -6817,17 +6813,17 @@
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P68" t="n">
-        <v>68</v>
+        <v>302</v>
       </c>
       <c r="Q68" t="n">
-        <v>228</v>
+        <v>472</v>
       </c>
       <c r="R68" t="n">
-        <v>296</v>
+        <v>774</v>
       </c>
       <c r="S68" t="inlineStr">
         <is>
@@ -6836,17 +6832,17 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>1839385378</t>
+          <t>1160428762</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1839385378</t>
+          <t>https://m.place.naver.com/place/1160428762</t>
         </is>
       </c>
       <c r="V68" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -6858,29 +6854,29 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>메디앤컬필라테스 정관점</t>
+          <t>폴인기구필라테스&amp;PT 부산 기장점</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>medincurljeonggwan@naver.com</t>
+          <t>cheryll1@naver.com</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>0507-1437-2824</t>
+          <t>0507-1434-0830</t>
         </is>
       </c>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 정관읍 정관로 563 광장메디컬 5층</t>
+          <t>부산광역시 기장군 기장읍 차성로 340 명성빌딩 5층</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/medincurljeonggwan</t>
+          <t>https://www.instagram.com/fallin_gijang</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -6895,7 +6891,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -6915,13 +6911,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>363</v>
+        <v>158</v>
       </c>
       <c r="Q69" t="n">
-        <v>114</v>
+        <v>479</v>
       </c>
       <c r="R69" t="n">
-        <v>477</v>
+        <v>637</v>
       </c>
       <c r="S69" t="inlineStr">
         <is>
@@ -6930,51 +6926,47 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>1558955764</t>
+          <t>1570283352</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1558955764</t>
+          <t>https://m.place.naver.com/place/1570283352</t>
         </is>
       </c>
       <c r="V69" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>우디짐PT</t>
+          <t>TOP PT GYM</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>woodygym@naver.com</t>
+          <t>topgym1@naver.com</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>070-8691-1998</t>
-        </is>
-      </c>
+      <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
-          <t>부산광역시 해운대구 세실로 87 6층 우디짐</t>
+          <t>부산광역시 기장군 정관읍 정관로 595</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/woodygym</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -6984,12 +6976,12 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -7005,17 +6997,17 @@
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P70" t="n">
-        <v>351</v>
+        <v>140</v>
       </c>
       <c r="Q70" t="n">
-        <v>373</v>
+        <v>0</v>
       </c>
       <c r="R70" t="n">
-        <v>724</v>
+        <v>140</v>
       </c>
       <c r="S70" t="inlineStr">
         <is>
@@ -7024,51 +7016,51 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>1696092453</t>
+          <t>1784014744</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1696092453</t>
+          <t>https://m.place.naver.com/place/1784014744</t>
         </is>
       </c>
       <c r="V70" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>건담짐 미국감성프리미엄헬스&amp;PT</t>
+          <t>버킷바디짐 여성전용 프리미엄PT 정관점</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>rlarjsdn12433@naver.com</t>
+          <t>bucketbodygym@naver.com</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>0507-1323-5243</t>
+          <t>0507-1341-9514</t>
         </is>
       </c>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
-          <t>부산광역시 동래구 온천천로 391 1층 건담짐</t>
+          <t>부산광역시 기장군 정관읍 정관로 561 정관타워 703호 버킷바디짐 여성전문 정관PT</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/rlarjsdn12433</t>
+          <t>https://blog.naver.com/bucketbodygym</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -7103,13 +7095,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>2858</v>
+        <v>115</v>
       </c>
       <c r="Q71" t="n">
-        <v>896</v>
+        <v>859</v>
       </c>
       <c r="R71" t="n">
-        <v>3754</v>
+        <v>974</v>
       </c>
       <c r="S71" t="inlineStr">
         <is>
@@ -7118,17 +7110,17 @@
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>1130935293</t>
+          <t>1083631392</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1130935293</t>
+          <t>https://m.place.naver.com/place/1083631392</t>
         </is>
       </c>
       <c r="V71" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -7140,34 +7132,38 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>하이리페움 피트니스</t>
+          <t>제로키니 그룹PT 일광점</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>high9970@naver.com</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr"/>
+          <t>pmk060@naver.com</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>jys@zerokini.co.kr</t>
+        </is>
+      </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>070-4222-6939</t>
+          <t>0507-1397-5606</t>
         </is>
       </c>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 일광읍 해빛4로 35 2층</t>
+          <t>부산광역시 기장군 일광읍 해빛로 39-30 5층</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>https://highlifeum.kr</t>
+          <t>https://www.zerokini.co.kr</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -7177,7 +7173,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -7188,7 +7184,7 @@
       <c r="M72" t="inlineStr"/>
       <c r="N72" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
@@ -7197,13 +7193,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>14</v>
+        <v>67</v>
       </c>
       <c r="Q72" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="R72" t="n">
-        <v>31</v>
+        <v>80</v>
       </c>
       <c r="S72" t="inlineStr">
         <is>
@@ -7212,46 +7208,46 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>1027296796</t>
+          <t>2003643168</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1027296796</t>
+          <t>https://m.place.naver.com/place/2003643168</t>
         </is>
       </c>
       <c r="V72" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>건축자재,용품</t>
+          <t>장비,기기</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>송정가설</t>
+          <t>BT비티아시바피티아시바파이프가설자재판매임대설치</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>cj141125@naver.com</t>
+          <t>hnco@naver.com</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>051-723-9927</t>
+          <t>070-4593-0268</t>
         </is>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 기장읍 내리1길 6</t>
+          <t>부산광역시 기장군 철마면 고촌리</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -7294,10 +7290,10 @@
         <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R73" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S73" t="inlineStr">
         <is>
@@ -7306,51 +7302,51 @@
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>37046367</t>
+          <t>1042095191</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37046367</t>
+          <t>https://m.place.naver.com/place/1042095191</t>
         </is>
       </c>
       <c r="V73" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>필라테스</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>상상피트니스 정관점</t>
+          <t>BB필라테스 일광점</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>sangsangft1@naver.com</t>
+          <t>bbpilates_ilguang@naver.com</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
-          <t>0507-1371-3383</t>
+          <t>0507-1432-0163</t>
         </is>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 정관읍 정관6로 39 메가박스 3층</t>
+          <t>부산광역시 기장군 일광읍 해송2로 11 미라벨 5층 501, 502호</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/sangsang_jeonggwan/</t>
+          <t>https://www.instagram.com/bbpilates_ilguang/</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -7385,13 +7381,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>913</v>
+        <v>67</v>
       </c>
       <c r="Q74" t="n">
-        <v>1229</v>
+        <v>104</v>
       </c>
       <c r="R74" t="n">
-        <v>2142</v>
+        <v>171</v>
       </c>
       <c r="S74" t="inlineStr">
         <is>
@@ -7400,51 +7396,51 @@
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>1193206895</t>
+          <t>1281840251</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1193206895</t>
+          <t>https://m.place.naver.com/place/1281840251</t>
         </is>
       </c>
       <c r="V74" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>올바른운동 해운대좌동점</t>
+          <t>강해짐 일광점 헬스&amp;PT</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>yesmyt@naver.com</t>
+          <t>gang_hae_gym@naver.com</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
-          <t>0507-1391-3259</t>
+          <t>0507-1357-1828</t>
         </is>
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
-          <t>부산광역시 해운대구 좌동순환로 181 5층</t>
+          <t>부산광역시 기장군 일광읍 해송4로 16 에코테라스 7층</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>https://abrtraining.kr/</t>
+          <t>https://pf.kakao.com/_AspkG</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -7459,7 +7455,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -7470,7 +7466,7 @@
       <c r="M75" t="inlineStr"/>
       <c r="N75" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
@@ -7479,13 +7475,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>278</v>
+        <v>184</v>
       </c>
       <c r="Q75" t="n">
-        <v>612</v>
+        <v>368</v>
       </c>
       <c r="R75" t="n">
-        <v>890</v>
+        <v>552</v>
       </c>
       <c r="S75" t="inlineStr">
         <is>
@@ -7494,17 +7490,17 @@
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>1715982137</t>
+          <t>1142407899</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1715982137</t>
+          <t>https://m.place.naver.com/place/1142407899</t>
         </is>
       </c>
       <c r="V75" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -7516,25 +7512,29 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>이리스 피트니스</t>
+          <t>헬스달리아 부산기장점</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>danairis_@naver.com</t>
+          <t>healthdahlia_pilates@naver.com</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
-      <c r="E76" t="inlineStr"/>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>0507-1349-4454</t>
+        </is>
+      </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
-          <t>부산광역시 기장군 정관읍 정관2로 39-14 7층 이리스피트니스</t>
+          <t>부산광역시 기장군 기장읍 차성동로126번길 23 1F 헬스달리아</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/danairis_</t>
+          <t>https://blog.naver.com/healthdahlia_pilates</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -7569,13 +7569,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>14</v>
+        <v>583</v>
       </c>
       <c r="Q76" t="n">
-        <v>8</v>
+        <v>88</v>
       </c>
       <c r="R76" t="n">
-        <v>22</v>
+        <v>671</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
@@ -7584,17 +7584,17 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>1706105476</t>
+          <t>1638524445</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1706105476</t>
+          <t>https://m.place.naver.com/place/1638524445</t>
         </is>
       </c>
       <c r="V76" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
